--- a/web/files/九龙-启德-Miami Quay II.xlsx
+++ b/web/files/九龙-启德-Miami Quay II.xlsx
@@ -2104,7 +2104,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -6291,38 +6291,30 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I82" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="n">
+        <v>15458000</v>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>24932</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K82" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L82" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K82" s="5" t="n">
+        <v>15458000</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>24932</v>
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
@@ -6331,7 +6323,7 @@
       </c>
       <c r="N82" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -6996,7 +6988,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -7688,7 +7680,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -8380,7 +8372,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -9072,7 +9064,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -9764,7 +9756,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -10456,7 +10448,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -11148,7 +11140,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -11840,7 +11832,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -12532,7 +12524,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -13224,7 +13216,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -13916,7 +13908,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -14608,7 +14600,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -15300,7 +15292,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -15992,7 +15984,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -16684,7 +16676,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -17376,7 +17368,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -19048,7 +19040,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H266" s="5" t="n">
@@ -21980,7 +21972,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H308" s="5" t="n">
@@ -22602,7 +22594,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H317" s="5" t="n">
@@ -22804,7 +22796,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H320" s="5" t="n">
@@ -23426,7 +23418,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="H329" s="5" t="n">
@@ -23628,7 +23620,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H332" s="5" t="n">
@@ -24250,7 +24242,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H341" s="5" t="n">
@@ -24452,7 +24444,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H344" s="5" t="n">
@@ -25074,7 +25066,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H353" s="5" t="n">
@@ -25276,7 +25268,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H356" s="5" t="n">
@@ -25898,7 +25890,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H365" s="5" t="n">
@@ -25960,7 +25952,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="H366" s="5" t="n">
@@ -26022,7 +26014,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H367" s="5" t="n">
@@ -26084,7 +26076,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H368" s="5" t="n">
@@ -26706,7 +26698,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H377" s="5" t="n">
@@ -26768,7 +26760,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H378" s="5" t="n">
@@ -26830,7 +26822,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H379" s="5" t="n">
@@ -26892,7 +26884,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H380" s="5" t="n">
@@ -27514,7 +27506,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H389" s="5" t="n">
@@ -27576,7 +27568,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H390" s="5" t="n">
@@ -27638,7 +27630,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H391" s="5" t="n">
@@ -27700,7 +27692,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H392" s="5" t="n">
@@ -28322,7 +28314,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H401" s="5" t="n">
@@ -28384,7 +28376,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H402" s="5" t="n">
@@ -28446,7 +28438,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H403" s="5" t="n">
@@ -28508,7 +28500,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H404" s="5" t="n">
@@ -29970,7 +29962,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H425" s="5" t="n">
@@ -30032,7 +30024,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H426" s="5" t="n">
@@ -30094,7 +30086,7 @@
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H427" s="5" t="n">
@@ -30156,7 +30148,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H428" s="5" t="n">
@@ -30568,7 +30560,7 @@
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H434" s="5" t="n">
@@ -30770,7 +30762,7 @@
       </c>
       <c r="G437" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H437" s="5" t="n">
@@ -30832,7 +30824,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H438" s="5" t="n">
@@ -30894,7 +30886,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H439" s="5" t="n">
@@ -30956,7 +30948,7 @@
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H440" s="5" t="n">
@@ -31368,7 +31360,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H446" s="5" t="n">
@@ -31570,7 +31562,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H449" s="5" t="n">
@@ -31632,7 +31624,7 @@
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H450" s="5" t="n">
@@ -31694,7 +31686,7 @@
       </c>
       <c r="G451" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H451" s="5" t="n">
@@ -31756,7 +31748,7 @@
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H452" s="5" t="n">
@@ -32168,7 +32160,7 @@
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="H458" s="5" t="n">
@@ -32300,7 +32292,7 @@
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H460" s="5" t="n">
@@ -32362,7 +32354,7 @@
       </c>
       <c r="G461" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H461" s="5" t="n">
@@ -32424,7 +32416,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H462" s="5" t="n">
@@ -32486,7 +32478,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H463" s="5" t="n">
@@ -32548,7 +32540,7 @@
       </c>
       <c r="G464" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H464" s="5" t="n">
@@ -32610,7 +32602,7 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="H465" s="5" t="n">
@@ -32952,7 +32944,7 @@
       </c>
       <c r="G470" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H470" s="5" t="n">
@@ -33084,7 +33076,7 @@
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H472" s="5" t="n">
@@ -33146,7 +33138,7 @@
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H473" s="5" t="n">
@@ -33208,7 +33200,7 @@
       </c>
       <c r="G474" s="3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H474" s="5" t="n">
@@ -33270,7 +33262,7 @@
       </c>
       <c r="G475" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H475" s="5" t="n">
@@ -33332,7 +33324,7 @@
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H476" s="5" t="n">
@@ -33394,7 +33386,7 @@
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H477" s="5" t="n">
@@ -33736,7 +33728,7 @@
       </c>
       <c r="G482" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H482" s="5" t="n">
@@ -33798,7 +33790,7 @@
       </c>
       <c r="G483" s="3" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H483" s="5" t="n">
@@ -33860,7 +33852,7 @@
       </c>
       <c r="G484" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H484" s="5" t="n">
@@ -33922,7 +33914,7 @@
       </c>
       <c r="G485" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H485" s="5" t="n">
@@ -33984,7 +33976,7 @@
       </c>
       <c r="G486" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H486" s="5" t="n">
@@ -34046,7 +34038,7 @@
       </c>
       <c r="G487" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H487" s="5" t="n">
@@ -34108,7 +34100,7 @@
       </c>
       <c r="G488" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H488" s="5" t="n">
@@ -34170,7 +34162,7 @@
       </c>
       <c r="G489" s="3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="H489" s="5" t="n">
@@ -34574,7 +34566,7 @@
       </c>
       <c r="G495" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H495" s="5" t="n">
@@ -34636,7 +34628,7 @@
       </c>
       <c r="G496" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H496" s="5" t="n">
@@ -34698,7 +34690,7 @@
       </c>
       <c r="G497" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H497" s="5" t="n">
@@ -34760,7 +34752,7 @@
       </c>
       <c r="G498" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H498" s="5" t="n">
@@ -34822,7 +34814,7 @@
       </c>
       <c r="G499" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H499" s="5" t="n">
@@ -34884,7 +34876,7 @@
       </c>
       <c r="G500" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H500" s="5" t="n">
@@ -34946,7 +34938,7 @@
       </c>
       <c r="G501" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H501" s="5" t="n">
@@ -35218,7 +35210,7 @@
       </c>
       <c r="G505" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H505" s="5" t="n">
@@ -35280,7 +35272,7 @@
       </c>
       <c r="G506" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H506" s="5" t="n">
@@ -35342,7 +35334,7 @@
       </c>
       <c r="G507" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H507" s="5" t="n">
@@ -35404,7 +35396,7 @@
       </c>
       <c r="G508" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H508" s="5" t="n">
@@ -35466,7 +35458,7 @@
       </c>
       <c r="G509" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H509" s="5" t="n">
@@ -35528,7 +35520,7 @@
       </c>
       <c r="G510" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H510" s="5" t="n">
@@ -35590,7 +35582,7 @@
       </c>
       <c r="G511" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H511" s="5" t="n">
@@ -38242,7 +38234,7 @@
       </c>
       <c r="G549" s="3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H549" s="5" t="n">
@@ -38374,7 +38366,7 @@
       </c>
       <c r="G551" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="H551" s="5" t="n">
@@ -38506,7 +38498,7 @@
       </c>
       <c r="G553" s="3" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H553" s="5" t="n">
@@ -38568,7 +38560,7 @@
       </c>
       <c r="G554" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H554" s="5" t="n">
@@ -38630,7 +38622,7 @@
       </c>
       <c r="G555" s="3" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="H555" s="5" t="n">
@@ -38832,7 +38824,7 @@
       </c>
       <c r="G558" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H558" s="5" t="n">
@@ -38894,7 +38886,7 @@
       </c>
       <c r="G559" s="3" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="H559" s="5" t="n">
@@ -38947,7 +38939,7 @@
         </is>
       </c>
       <c r="E560" s="4" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F560" s="3" t="inlineStr">
         <is>
@@ -38956,14 +38948,14 @@
       </c>
       <c r="G560" s="3" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="H560" s="5" t="n">
         <v>7890000</v>
       </c>
       <c r="I560" s="5" t="n">
-        <v>25700</v>
+        <v>25617</v>
       </c>
       <c r="J560" s="3" t="inlineStr">
         <is>
@@ -38974,7 +38966,7 @@
         <v>7890000</v>
       </c>
       <c r="L560" s="5" t="n">
-        <v>25700</v>
+        <v>25617</v>
       </c>
       <c r="M560" s="3" t="inlineStr">
         <is>
@@ -39018,7 +39010,7 @@
       </c>
       <c r="G561" s="3" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="H561" s="5" t="n">
@@ -39080,7 +39072,7 @@
       </c>
       <c r="G562" s="3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="H562" s="5" t="n">
@@ -39142,7 +39134,7 @@
       </c>
       <c r="G563" s="3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="H563" s="5" t="n">
@@ -39204,7 +39196,7 @@
       </c>
       <c r="G564" s="3" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H564" s="5" t="n">
@@ -39266,7 +39258,7 @@
       </c>
       <c r="G565" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H565" s="5" t="n">
@@ -39328,7 +39320,7 @@
       </c>
       <c r="G566" s="3" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H566" s="5" t="n">
@@ -39390,7 +39382,7 @@
       </c>
       <c r="G567" s="3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="H567" s="5" t="n">
@@ -39452,7 +39444,7 @@
       </c>
       <c r="G568" s="3" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H568" s="5" t="n">
@@ -39514,7 +39506,7 @@
       </c>
       <c r="G569" s="3" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="H569" s="5" t="n">
@@ -39576,7 +39568,7 @@
       </c>
       <c r="G570" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H570" s="5" t="n">
@@ -39638,7 +39630,7 @@
       </c>
       <c r="G571" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H571" s="5" t="n">
@@ -39700,7 +39692,7 @@
       </c>
       <c r="G572" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H572" s="5" t="n">
@@ -39762,7 +39754,7 @@
       </c>
       <c r="G573" s="3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="H573" s="5" t="n">
@@ -39871,7 +39863,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -39881,7 +39873,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -40050,7 +40042,7 @@
           <t>A | 620呎 (3房)
 $1573万
 $25,371/呎
-(26年-07月-13日)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -40567,12 +40559,12 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>A | 620呎 (3房)
-招标单位
--
-(在售)</t>
+$1546万
+$24,932/呎
+(26年-07月-23日)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
@@ -40659,7 +40651,7 @@
           <t>A | 620呎 (3房)
 $1542万
 $24,869/呎
-(26年-07月-14日)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -40746,7 +40738,7 @@
           <t>A | 620呎 (3房)
 $1538万
 $24,806/呎
-(26年-07月-19日)</t>
+(26年-07月-20日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -40833,7 +40825,7 @@
           <t>A | 620呎 (3房)
 $1534万
 $24,745/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -40920,7 +40912,7 @@
           <t>A | 620呎 (3房)
 $1530万
 $24,684/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -41007,7 +40999,7 @@
           <t>A | 620呎 (3房)
 $1523万
 $24,561/呎
-(26年-07月-08日)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -41094,7 +41086,7 @@
           <t>A | 620呎 (3房)
 $1519万
 $24,500/呎
-(26年-06月-15日)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -41181,7 +41173,7 @@
           <t>A | 620呎 (3房)
 $1515万
 $24,437/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -41268,7 +41260,7 @@
           <t>A | 620呎 (3房)
 $1511万
 $24,377/呎
-(26年-07月-13日)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -41355,7 +41347,7 @@
           <t>A | 620呎 (3房)
 $1508万
 $24,318/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -41442,7 +41434,7 @@
           <t>A | 620呎 (3房)
 $1504万
 $24,256/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -41529,7 +41521,7 @@
           <t>A | 620呎 (3房)
 $1500万
 $24,195/呎
-(26年-06月-25日)</t>
+(26年-07月-28日)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -41616,7 +41608,7 @@
           <t>A | 620呎 (3房)
 $1496万
 $24,135/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -41703,7 +41695,7 @@
           <t>A | 620呎 (3房)
 $1489万
 $24,015/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
@@ -41790,7 +41782,7 @@
           <t>A | 620呎 (3房)
 $1485万
 $23,955/呎
-(26年-07月-20日)</t>
+(26年-07月-21日)</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
@@ -41877,7 +41869,7 @@
           <t>A | 620呎 (3房)
 $1482万
 $23,895/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
@@ -41964,7 +41956,7 @@
           <t>A | 620呎 (3房)
 $1478万
 $23,835/呎
-(26年-06月-08日)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
@@ -42368,7 +42360,7 @@
           <t>A | 1426呎 (4+房)
 $4634万
 $32,500/呎
-(25年-07月-09日)</t>
+(25年-07月-10日)</t>
         </is>
       </c>
       <c r="C5" s="23" t="inlineStr"/>
@@ -42800,7 +42792,7 @@
           <t>G | 435呎 (2房)
 $1008万
 $23,166/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="I9" s="21" t="inlineStr">
@@ -42903,7 +42895,7 @@
           <t>G | 435呎 (2房)
 $1005万
 $23,108/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="I10" s="21" t="inlineStr">
@@ -42927,7 +42919,7 @@
           <t>K | 319呎 (1房)
 $725万
 $22,724/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="L10" s="21" t="inlineStr">
@@ -43006,7 +42998,7 @@
           <t>G | 435呎 (2房)
 $1003万
 $23,051/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="I11" s="21" t="inlineStr">
@@ -43030,7 +43022,7 @@
           <t>K | 319呎 (1房)
 $723万
 $22,668/呎
-(26年-05月-03日)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="L11" s="21" t="inlineStr">
@@ -43109,7 +43101,7 @@
           <t>G | 435呎 (2房)
 $1000万
 $22,993/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="I12" s="21" t="inlineStr">
@@ -43133,7 +43125,7 @@
           <t>K | 319呎 (1房)
 $721万
 $22,611/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="L12" s="21" t="inlineStr">
@@ -43212,7 +43204,7 @@
           <t>G | 435呎 (2房)
 $998万
 $22,936/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="I13" s="21" t="inlineStr">
@@ -43236,7 +43228,7 @@
           <t>K | 319呎 (1房)
 $720万
 $22,555/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="L13" s="21" t="inlineStr">
@@ -43315,7 +43307,7 @@
           <t>G | 435呎 (2房)
 $995万
 $22,878/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="I14" s="22" t="inlineStr">
@@ -43323,7 +43315,7 @@
           <t>H | 454呎 (2房)
 $1023万
 $22,529/呎
-(26年-04月-27日)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="J14" s="22" t="inlineStr">
@@ -43331,7 +43323,7 @@
           <t>J | 326呎 (1房)
 $728万
 $22,347/呎
-(26年-04月-28日)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="K14" s="22" t="inlineStr">
@@ -43339,7 +43331,7 @@
           <t>K | 319呎 (1房)
 $718万
 $22,498/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="L14" s="21" t="inlineStr">
@@ -43418,7 +43410,7 @@
           <t>G | 435呎 (2房)
 $993万
 $22,823/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="I15" s="22" t="inlineStr">
@@ -43426,7 +43418,7 @@
           <t>H | 454呎 (2房)
 $1020万
 $22,471/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="J15" s="22" t="inlineStr">
@@ -43434,7 +43426,7 @@
           <t>J | 326呎 (1房)
 $727万
 $22,294/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="K15" s="22" t="inlineStr">
@@ -43442,7 +43434,7 @@
           <t>K | 319呎 (1房)
 $716万
 $22,442/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="L15" s="21" t="inlineStr">
@@ -43521,7 +43513,7 @@
           <t>G | 435呎 (2房)
 $990万
 $22,763/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="I16" s="22" t="inlineStr">
@@ -43529,7 +43521,7 @@
           <t>H | 454呎 (2房)
 $1018万
 $22,416/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="J16" s="22" t="inlineStr">
@@ -43537,7 +43529,7 @@
           <t>J | 326呎 (1房)
 $725万
 $22,236/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="K16" s="22" t="inlineStr">
@@ -43545,7 +43537,7 @@
           <t>K | 319呎 (1房)
 $714万
 $22,389/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="L16" s="21" t="inlineStr">
@@ -43624,7 +43616,7 @@
           <t>G | 435呎 (2房)
 $985万
 $22,653/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="I17" s="22" t="inlineStr">
@@ -43632,7 +43624,7 @@
           <t>H | 454呎 (2房)
 $1013万
 $22,306/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="J17" s="22" t="inlineStr">
@@ -43640,7 +43632,7 @@
           <t>J | 326呎 (1房)
 $721万
 $22,126/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="K17" s="22" t="inlineStr">
@@ -43648,7 +43640,7 @@
           <t>K | 319呎 (1房)
 $711万
 $22,276/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="L17" s="21" t="inlineStr">
@@ -43782,7 +43774,7 @@
           <t>A | 482呎 (2房)
 $1240万
 $25,728/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -43830,7 +43822,7 @@
           <t>G | 435呎 (2房)
 $980万
 $22,540/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="I19" s="22" t="inlineStr">
@@ -43838,7 +43830,7 @@
           <t>H | 454呎 (2房)
 $1008万
 $22,194/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="J19" s="22" t="inlineStr">
@@ -43846,7 +43838,7 @@
           <t>J | 326呎 (1房)
 $718万
 $22,015/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="K19" s="22" t="inlineStr">
@@ -43854,7 +43846,7 @@
           <t>K | 319呎 (1房)
 $707万
 $22,163/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="L19" s="21" t="inlineStr">
@@ -43885,7 +43877,7 @@
           <t>A | 482呎 (2房)
 $1237万
 $25,666/呎
-(26年-06月-11日)</t>
+(26年-06月-12日)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -43933,7 +43925,7 @@
           <t>G | 435呎 (2房)
 $978万
 $22,483/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="I20" s="22" t="inlineStr">
@@ -43941,7 +43933,7 @@
           <t>H | 454呎 (2房)
 $1005万
 $22,139/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="J20" s="22" t="inlineStr">
@@ -43949,7 +43941,7 @@
           <t>J | 326呎 (1房)
 $716万
 $21,960/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="K20" s="22" t="inlineStr">
@@ -43957,7 +43949,7 @@
           <t>K | 319呎 (1房)
 $705万
 $22,110/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="L20" s="21" t="inlineStr">
@@ -43988,7 +43980,7 @@
           <t>A | 482呎 (2房)
 $1234万
 $25,602/呎
-(26年-06月-15日)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -44036,7 +44028,7 @@
           <t>G | 435呎 (2房)
 $976万
 $22,425/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="I21" s="22" t="inlineStr">
@@ -44044,7 +44036,7 @@
           <t>H | 454呎 (2房)
 $1002万
 $22,081/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="J21" s="22" t="inlineStr">
@@ -44052,7 +44044,7 @@
           <t>J | 326呎 (1房)
 $714万
 $21,908/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="K21" s="22" t="inlineStr">
@@ -44060,7 +44052,7 @@
           <t>K | 319呎 (1房)
 $704万
 $22,053/呎
-(26年-05月-11日)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="L21" s="21" t="inlineStr">
@@ -44091,7 +44083,7 @@
           <t>A | 482呎 (2房)
 $1231万
 $25,537/呎
-(26年-06月-14日)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -44131,7 +44123,7 @@
           <t>F | 335呎 (1房)
 $699万
 $20,863/呎
-(26年-03月-16日)</t>
+(26年-03月-17日)</t>
         </is>
       </c>
       <c r="H22" s="22" t="inlineStr">
@@ -44139,7 +44131,7 @@
           <t>G | 435呎 (2房)
 $973万
 $22,372/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="I22" s="22" t="inlineStr">
@@ -44147,7 +44139,7 @@
           <t>H | 454呎 (2房)
 $1000万
 $22,029/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="J22" s="22" t="inlineStr">
@@ -44155,7 +44147,7 @@
           <t>J | 326呎 (1房)
 $712万
 $21,850/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="K22" s="22" t="inlineStr">
@@ -44163,7 +44155,7 @@
           <t>K | 318呎 (1房)
 $702万
 $22,069/呎
-(26年-04月-19日)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="L22" s="22" t="inlineStr">
@@ -44171,7 +44163,7 @@
           <t>L | 463呎 (2房)
 $1127万
 $24,346/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="M22" s="21" t="inlineStr">
@@ -44194,7 +44186,7 @@
           <t>A | 482呎 (2房)
 $1228万
 $25,473/呎
-(26年-07月-08日)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -44234,7 +44226,7 @@
           <t>F | 335呎 (1房)
 $697万
 $20,809/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="H23" s="22" t="inlineStr">
@@ -44242,7 +44234,7 @@
           <t>G | 435呎 (2房)
 $971万
 $22,315/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="I23" s="22" t="inlineStr">
@@ -44250,7 +44242,7 @@
           <t>H | 454呎 (2房)
 $998万
 $21,974/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="J23" s="22" t="inlineStr">
@@ -44258,7 +44250,7 @@
           <t>J | 326呎 (1房)
 $711万
 $21,798/呎
-(26年-04月-12日)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="K23" s="22" t="inlineStr">
@@ -44266,7 +44258,7 @@
           <t>K | 319呎 (1房)
 $700万
 $21,944/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="L23" s="22" t="inlineStr">
@@ -44274,7 +44266,7 @@
           <t>L | 463呎 (2房)
 $1124万
 $24,285/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="M23" s="21" t="inlineStr">
@@ -44337,7 +44329,7 @@
           <t>F | 335呎 (1房)
 $695万
 $20,755/呎
-(26年-05月-04日)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="H24" s="22" t="inlineStr">
@@ -44345,7 +44337,7 @@
           <t>G | 435呎 (2房)
 $968万
 $22,260/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="I24" s="22" t="inlineStr">
@@ -44353,7 +44345,7 @@
           <t>H | 454呎 (2房)
 $995万
 $21,919/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="J24" s="22" t="inlineStr">
@@ -44361,7 +44353,7 @@
           <t>J | 326呎 (1房)
 $709万
 $21,742/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="K24" s="22" t="inlineStr">
@@ -44369,7 +44361,7 @@
           <t>K | 319呎 (1房)
 $698万
 $21,887/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="L24" s="22" t="inlineStr">
@@ -44377,7 +44369,7 @@
           <t>L | 463呎 (2房)
 $1122万
 $24,227/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="M24" s="22" t="inlineStr">
@@ -44385,7 +44377,7 @@
           <t>M | 251呎 (开放式)
 $593万
 $23,637/呎
-(26年-04月-09日)</t>
+(26年-04月-10日)</t>
         </is>
       </c>
     </row>
@@ -44426,7 +44418,7 @@
           <t>F | 335呎 (1房)
 $692万
 $20,654/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="H25" s="22" t="inlineStr">
@@ -44434,7 +44426,7 @@
           <t>G | 435呎 (2房)
 $964万
 $22,149/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="I25" s="22" t="inlineStr">
@@ -44442,7 +44434,7 @@
           <t>H | 454呎 (2房)
 $990万
 $21,808/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="J25" s="22" t="inlineStr">
@@ -44450,7 +44442,7 @@
           <t>J | 326呎 (1房)
 $705万
 $21,635/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="K25" s="22" t="inlineStr">
@@ -44458,7 +44450,7 @@
           <t>K | 319呎 (1房)
 $695万
 $21,781/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="L25" s="22" t="inlineStr">
@@ -44466,7 +44458,7 @@
           <t>L | 463呎 (2房)
 $1116万
 $24,106/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="M25" s="22" t="inlineStr">
@@ -44474,7 +44466,7 @@
           <t>M | 255呎 (开放式)
 $593万
 $23,255/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
     </row>
@@ -44515,7 +44507,7 @@
           <t>F | 335呎 (1房)
 $690万
 $20,603/呎
-(26年-05月-11日)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="H26" s="22" t="inlineStr">
@@ -44523,7 +44515,7 @@
           <t>G | 435呎 (2房)
 $961万
 $22,092/呎
-(26年-04月-19日)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="I26" s="22" t="inlineStr">
@@ -44531,7 +44523,7 @@
           <t>H | 454呎 (2房)
 $988万
 $21,756/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="J26" s="22" t="inlineStr">
@@ -44539,7 +44531,7 @@
           <t>J | 326呎 (1房)
 $704万
 $21,580/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="K26" s="22" t="inlineStr">
@@ -44547,7 +44539,7 @@
           <t>K | 319呎 (1房)
 $693万
 $21,724/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="L26" s="22" t="inlineStr">
@@ -44555,7 +44547,7 @@
           <t>L | 463呎 (2房)
 $1113万
 $24,045/呎
-(26年-06月-17日)</t>
+(26年-06月-18日)</t>
         </is>
       </c>
       <c r="M26" s="22" t="inlineStr">
@@ -44563,7 +44555,7 @@
           <t>M | 255呎 (开放式)
 $592万
 $23,196/呎
-(26年-06月-10日)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
     </row>
@@ -45021,7 +45013,7 @@
           <t>A | 491呎 (2房)
 $1360万
 $27,699/呎
-(25年-12月-07日)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -45037,7 +45029,7 @@
           <t>C | 308呎 (1房)
 $846万
 $27,468/呎
-(26年-06月-15日)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -45053,7 +45045,7 @@
           <t>E | 494呎 (2房)
 $1360万
 $27,530/呎
-(25年-11月-25日)</t>
+(25年-11月-26日)</t>
         </is>
       </c>
     </row>
@@ -45068,7 +45060,7 @@
           <t>A | 491呎 (2房)
 $1282万
 $26,102/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -45092,7 +45084,7 @@
           <t>D | 308呎 (1房)
 $809万
 $26,266/呎
-(26年-01月-25日)</t>
+(26年-01月-26日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -45100,7 +45092,7 @@
           <t>E | 494呎 (2房)
 $1326万
 $26,834/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -45115,7 +45107,7 @@
           <t>A | 491呎 (2房)
 $1274万
 $25,955/呎
-(25年-12月-01日)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -45123,7 +45115,7 @@
           <t>B | 307呎 (1房)
 $789万
 $25,700/呎
-(25年-12月-01日)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -45131,15 +45123,15 @@
           <t>C | 307呎 (1房)
 $789万
 $25,700/呎
-(25年-11月-30日)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
         <is>
-          <t>D | 307呎 (1房)
+          <t>D | 308呎 (1房)
 $789万
-$25,700/呎
-(25年-11月-30日)</t>
+$25,617/呎
+(25年-12月-01日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -45147,7 +45139,7 @@
           <t>E | 494呎 (2房)
 $1308万
 $26,474/呎
-(25年-11月-30日)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
     </row>
@@ -45162,7 +45154,7 @@
           <t>A | 491呎 (2房)
 $1268万
 $25,825/呎
-(25年-12月-07日)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -45170,7 +45162,7 @@
           <t>B | 307呎 (1房)
 $785万
 $25,570/呎
-(25年-12月-04日)</t>
+(25年-12月-05日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -45178,7 +45170,7 @@
           <t>C | 307呎 (1房)
 $785万
 $25,570/呎
-(25年-12月-07日)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -45186,7 +45178,7 @@
           <t>D | 308呎 (1房)
 $785万
 $25,487/呎
-(26年-03月-04日)</t>
+(26年-03月-05日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -45194,7 +45186,7 @@
           <t>E | 494呎 (2房)
 $1301万
 $26,342/呎
-(25年-12月-07日)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
     </row>
@@ -45209,7 +45201,7 @@
           <t>A | 453呎 (2房)
 $1188万
 $26,225/呎
-(25年-09月-01日)</t>
+(25年-09月-02日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -45217,7 +45209,7 @@
           <t>B | 308呎 (1房)
 $781万
 $25,360/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -45225,7 +45217,7 @@
           <t>C | 308呎 (1房)
 $781万
 $25,360/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -45233,7 +45225,7 @@
           <t>D | 308呎 (1房)
 $784万
 $25,445/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -45241,7 +45233,7 @@
           <t>E | 456呎 (2房)
 $1250万
 $27,412/呎
-(25年-07月-14日)</t>
+(25年-07月-15日)</t>
         </is>
       </c>
     </row>

--- a/web/files/九龙-启德-Miami Quay II.xlsx
+++ b/web/files/九龙-启德-Miami Quay II.xlsx
@@ -9756,7 +9756,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -40999,7 +40999,7 @@
           <t>A | 620呎 (3房)
 $1523万
 $24,561/呎
-(26年-07月-09日)</t>
+(26年-08月-03日)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">

--- a/web/files/九龙-启德-Miami Quay II.xlsx
+++ b/web/files/九龙-启德-Miami Quay II.xlsx
@@ -11832,7 +11832,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -41260,7 +41260,7 @@
           <t>A | 620呎 (3房)
 $1511万
 $24,377/呎
-(26年-07月-14日)</t>
+(26年-08月-06日)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">

--- a/web/files/九龙-启德-Miami Quay II.xlsx
+++ b/web/files/九龙-启德-Miami Quay II.xlsx
@@ -7680,7 +7680,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -40738,7 +40738,7 @@
           <t>A | 620呎 (3房)
 $1538万
 $24,806/呎
-(26年-07月-20日)</t>
+(26年-08月-10日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">

--- a/web/files/九龙-启德-Miami Quay II.xlsx
+++ b/web/files/九龙-启德-Miami Quay II.xlsx
@@ -6296,7 +6296,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -40564,7 +40564,7 @@
           <t>A | 620呎 (3房)
 $1546万
 $24,932/呎
-(26年-07月-23日)</t>
+(26年-08月-18日)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">

--- a/web/files/九龙-启德-Miami Quay II.xlsx
+++ b/web/files/九龙-启德-Miami Quay II.xlsx
@@ -5591,38 +5591,30 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I72" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="n">
+        <v>15761000</v>
+      </c>
+      <c r="I72" s="5" t="n">
+        <v>25421</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K72" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L72" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K72" s="5" t="n">
+        <v>15761000</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>25421</v>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
@@ -5631,7 +5623,7 @@
       </c>
       <c r="N72" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -39863,7 +39855,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -39873,7 +39865,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -40472,12 +40464,12 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>A | 620呎 (3房)
-招标单位
--
-(在售)</t>
+$1576万
+$25,421/呎
+(26年-08月-23日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">

--- a/web/files/九龙-启德-Miami Quay II.xlsx
+++ b/web/files/九龙-启德-Miami Quay II.xlsx
@@ -660,7 +660,7 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -32337,7 +32337,7 @@
         </is>
       </c>
       <c r="E461" s="4" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F461" s="3" t="inlineStr">
         <is>
@@ -32353,7 +32353,7 @@
         <v>7018000</v>
       </c>
       <c r="I461" s="5" t="n">
-        <v>22069</v>
+        <v>22000</v>
       </c>
       <c r="J461" s="3" t="inlineStr">
         <is>
@@ -32364,7 +32364,7 @@
         <v>7018000</v>
       </c>
       <c r="L461" s="5" t="n">
-        <v>22069</v>
+        <v>22000</v>
       </c>
       <c r="M461" s="3" t="inlineStr">
         <is>
@@ -34491,34 +34491,34 @@
       </c>
       <c r="F494" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G494" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="H494" s="5" t="n">
-        <v>13917000</v>
+        <v>12247000</v>
       </c>
       <c r="I494" s="5" t="n">
-        <v>28873</v>
+        <v>25409</v>
       </c>
       <c r="J494" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K494" s="5" t="n">
-        <v>12246960</v>
+        <v>12247000</v>
       </c>
       <c r="L494" s="5" t="n">
         <v>25409</v>
       </c>
       <c r="M494" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N494" s="3" t="inlineStr">
@@ -42250,7 +42250,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -42260,7 +42260,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>77</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -44144,9 +44144,9 @@
       </c>
       <c r="K22" s="22" t="inlineStr">
         <is>
-          <t>K | 318呎 (1房)
+          <t>K | 319呎 (1房)
 $702万
-$22,069/呎
+$22,000/呎
 (26年-04月-20日)</t>
         </is>
       </c>
@@ -44276,12 +44276,12 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B24" s="20" t="inlineStr">
+      <c r="B24" s="22" t="inlineStr">
         <is>
           <t>A | 482呎 (2房)
-$1392万
-$28,873/呎
-(在售)</t>
+$1225万
+$25,409/呎
+(26年-08月-26日)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
